--- a/course_docs/PHY_905_comp_astro_schedule_Spring_2026.v2.xlsx
+++ b/course_docs/PHY_905_comp_astro_schedule_Spring_2026.v2.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/course_docs/PHY_905_comp_astro_schedule_Spring_2026.v2.xlsx
+++ b/course_docs/PHY_905_comp_astro_schedule_Spring_2026.v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bwoshea/Desktop/SYNCHED/Current Projects/PHY 905 - comp astro - Spring 2026/Computational_Astro_Spring_2026/course_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6AC2C6-5010-DA4E-9CCB-85EB0C550C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8AAE63-11E4-3049-BC31-D09E74904428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34740" yWindow="1900" windowWidth="29440" windowHeight="17820" xr2:uid="{1DD546E5-30D0-C340-B1F1-F7B464A6F5C2}"/>
+    <workbookView xWindow="980" yWindow="760" windowWidth="29440" windowHeight="17820" xr2:uid="{1DD546E5-30D0-C340-B1F1-F7B464A6F5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
   <si>
     <t>Spring 2026 course calendar - draft version</t>
   </si>
@@ -125,9 +125,6 @@
     <t>4/27-5/1</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>FINAL EXAM WEEK - Final presentations!</t>
   </si>
   <si>
@@ -155,21 +152,12 @@
     <t>Homework #3 due Friday 4/10</t>
   </si>
   <si>
-    <t>Homework #4 due Friday 5/1 (last day of finals week)</t>
-  </si>
-  <si>
-    <t>Project proposal due Monday 3/16</t>
-  </si>
-  <si>
     <t>Project update #1 due Monday 3/30</t>
   </si>
   <si>
     <t>Project update #2 due Wednesday 4/15</t>
   </si>
   <si>
-    <t>Project presentations, code demos, writeup, etc. due finals week (immediately before final exam session)</t>
-  </si>
-  <si>
     <t>Major deadlines (semester project deadlines are tentative)</t>
   </si>
   <si>
@@ -179,9 +167,6 @@
     <t xml:space="preserve">Brian out of town </t>
   </si>
   <si>
-    <t>May move parallel computing before Feigelson Ch. 2</t>
-  </si>
-  <si>
     <t>Homework #1 due Sunday 2/16</t>
   </si>
   <si>
@@ -189,6 +174,18 @@
   </si>
   <si>
     <t>Parabolic PDEs (Diffusion)</t>
+  </si>
+  <si>
+    <t>Friday 5/1, 7:45 a.m.</t>
+  </si>
+  <si>
+    <t>Project proposal due Wednesday 3/18</t>
+  </si>
+  <si>
+    <t>Homework #4 due Friday 5/1 (last day of finals week).  This is a firm deadline!</t>
+  </si>
+  <si>
+    <t>Project presentations, code demos, etc. due finals week (immediately before final exam session).  This is a firm deadline!</t>
   </si>
 </sst>
 </file>
@@ -659,7 +656,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -776,7 +773,7 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -825,7 +822,7 @@
         <v>18</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -840,7 +837,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="1"/>
@@ -856,7 +853,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="1"/>
@@ -872,7 +869,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="1"/>
@@ -932,7 +929,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="1"/>
@@ -948,10 +945,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1"/>
     </row>
@@ -966,10 +963,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1"/>
     </row>
@@ -1003,9 +1000,7 @@
         <v>21</v>
       </c>
       <c r="E24" s="10"/>
-      <c r="F24" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
@@ -1037,7 +1032,7 @@
         <v>23</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F26" s="1"/>
     </row>
@@ -1087,7 +1082,7 @@
         <v>26</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F29" s="1"/>
     </row>
@@ -1102,11 +1097,11 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1123,7 +1118,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F31" s="1"/>
     </row>
@@ -1151,7 +1146,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="1"/>
@@ -1162,7 +1157,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="1"/>
       <c r="E34" s="9" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F34" s="1"/>
     </row>
@@ -1171,14 +1166,14 @@
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F35" s="1"/>
     </row>

--- a/course_docs/PHY_905_comp_astro_schedule_Spring_2026.v2.xlsx
+++ b/course_docs/PHY_905_comp_astro_schedule_Spring_2026.v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bwoshea/Desktop/SYNCHED/Current Projects/PHY 905 - comp astro - Spring 2026/Computational_Astro_Spring_2026/course_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8AAE63-11E4-3049-BC31-D09E74904428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6A9C44-44E8-8C43-9713-99F053A38ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="760" windowWidth="29440" windowHeight="17820" xr2:uid="{1DD546E5-30D0-C340-B1F1-F7B464A6F5C2}"/>
+    <workbookView xWindow="800" yWindow="760" windowWidth="29440" windowHeight="17820" xr2:uid="{1DD546E5-30D0-C340-B1F1-F7B464A6F5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>Spring 2026 course calendar - draft version</t>
   </si>
@@ -143,9 +143,6 @@
     <t>No class - Brian's out of town!</t>
   </si>
   <si>
-    <t>Time series analysis, Part II; class wrapup.</t>
-  </si>
-  <si>
     <t>Homework #2 due Friday 3/13</t>
   </si>
   <si>
@@ -186,6 +183,12 @@
   </si>
   <si>
     <t>Project presentations, code demos, etc. due finals week (immediately before final exam session).  This is a firm deadline!</t>
+  </si>
+  <si>
+    <t>Time series analysis, Part II</t>
+  </si>
+  <si>
+    <t>"Big Data", ML, and AI in astronomy and astrophysics.  Also class wrapup.</t>
   </si>
 </sst>
 </file>
@@ -656,7 +659,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -773,7 +776,7 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -822,7 +825,7 @@
         <v>18</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -853,7 +856,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="1"/>
@@ -869,7 +872,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="1"/>
@@ -948,7 +951,7 @@
         <v>32</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1"/>
     </row>
@@ -966,7 +969,7 @@
         <v>33</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" s="1"/>
     </row>
@@ -1032,7 +1035,7 @@
         <v>23</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F26" s="1"/>
     </row>
@@ -1082,7 +1085,7 @@
         <v>26</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F29" s="1"/>
     </row>
@@ -1093,15 +1096,13 @@
       <c r="B30" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="2">
-        <v>25</v>
-      </c>
+      <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1112,13 +1113,13 @@
         <v>5</v>
       </c>
       <c r="C31" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F31" s="1"/>
     </row>
@@ -1130,7 +1131,10 @@
         <v>4</v>
       </c>
       <c r="C32" s="5">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="1"/>
@@ -1143,10 +1147,10 @@
         <v>5</v>
       </c>
       <c r="C33" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="1"/>
@@ -1157,7 +1161,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="1"/>
       <c r="E34" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F34" s="1"/>
     </row>
@@ -1166,14 +1170,14 @@
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F35" s="1"/>
     </row>

--- a/course_docs/PHY_905_comp_astro_schedule_Spring_2026.v2.xlsx
+++ b/course_docs/PHY_905_comp_astro_schedule_Spring_2026.v2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bwoshea/Desktop/SYNCHED/Current Projects/PHY 905 - comp astro - Spring 2026/Computational_Astro_Spring_2026/course_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6A9C44-44E8-8C43-9713-99F053A38ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE15A59-BE4F-F444-916B-116918049BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="760" windowWidth="29440" windowHeight="17820" xr2:uid="{1DD546E5-30D0-C340-B1F1-F7B464A6F5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -158,12 +158,6 @@
     <t>Major deadlines (semester project deadlines are tentative)</t>
   </si>
   <si>
-    <t>Brian out of town; Ben Wibking tentatively covering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian out of town </t>
-  </si>
-  <si>
     <t>Homework #1 due Sunday 2/16</t>
   </si>
   <si>
@@ -189,6 +183,12 @@
   </si>
   <si>
     <t>"Big Data", ML, and AI in astronomy and astrophysics.  Also class wrapup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Brian out of town; Ben Wibking teaching</t>
   </si>
 </sst>
 </file>
@@ -776,7 +776,7 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -825,7 +825,7 @@
         <v>18</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -856,7 +856,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="1"/>
@@ -872,7 +872,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="1"/>
@@ -922,8 +922,8 @@
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="6">
-        <v>45726</v>
+      <c r="A20" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>4</v>
@@ -969,7 +969,7 @@
         <v>33</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F22" s="1"/>
     </row>
@@ -1101,9 +1101,7 @@
         <v>34</v>
       </c>
       <c r="E30" s="4"/>
-      <c r="F30" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
@@ -1134,7 +1132,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="1"/>
@@ -1150,7 +1148,7 @@
         <v>27</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="1"/>
@@ -1161,7 +1159,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="1"/>
       <c r="E34" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F34" s="1"/>
     </row>
@@ -1170,19 +1168,19 @@
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F35" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="62" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup scale="66" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>